--- a/Claude outputs/Tableau-couleurs-Planning-Chantiers.xlsx
+++ b/Claude outputs/Tableau-couleurs-Planning-Chantiers.xlsx
@@ -89,7 +89,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="24">
+  <fills count="42">
     <fill>
       <patternFill/>
     </fill>
@@ -205,6 +205,94 @@
       <patternFill patternType="solid">
         <fgColor rgb="003FA15A"/>
       </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0010161D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DFDFDF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001C2530"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F0F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00171F28"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D7DAD2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002B3540"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A2129"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004A5661"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF1F4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0057616B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009AA7B3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008B93A0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0066717C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00141814"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00182129"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid"/>
     </fill>
   </fills>
   <borders count="2">
@@ -233,7 +321,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -344,6 +432,78 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="23" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="34" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="36" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="37" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="38" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="39" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="40" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="41" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -830,7 +990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1404,28 +1564,406 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="52" t="n"/>
-      <c r="B15" s="53" t="inlineStr">
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Fond général de l'appli</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Le fond derrière tout, tout en haut de l'écran (bandeau du haut, zone au-dessus du planning).</t>
+        </is>
+      </c>
+      <c r="D15" s="52" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E15" s="53" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="F15" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G15" s="55" t="inlineStr">
+        <is>
+          <t>#10161D</t>
+        </is>
+      </c>
+      <c r="H15" s="12" t="n"/>
+      <c r="I15" s="13" t="inlineStr"/>
+    </row>
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Fond des cases</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Le fond de TOUTES les cases du planning, des en-têtes de colonnes (jours) et des étiquettes de ligne (noms des personnes) — la couleur la plus présente de la grille.</t>
+        </is>
+      </c>
+      <c r="D16" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E16" s="57" t="inlineStr">
+        <is>
+          <t>#DFDFDF</t>
+        </is>
+      </c>
+      <c r="F16" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G16" s="59" t="inlineStr">
+        <is>
+          <t>#1C2530</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="n"/>
+      <c r="I16" s="13" t="inlineStr"/>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Fond secondaire (coin, étiquettes spéciales)</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Fond du coin en haut à gauche de la grille, des lignes "spéciales" (section Personnel/Intervenants), et de la petite ligne matin/après-midi en mode compact.</t>
+        </is>
+      </c>
+      <c r="D17" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E17" s="61" t="inlineStr">
+        <is>
+          <t>#F0F0F0</t>
+        </is>
+      </c>
+      <c r="F17" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G17" s="63" t="inlineStr">
+        <is>
+          <t>#171F28</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="n"/>
+      <c r="I17" s="13" t="inlineStr"/>
+    </row>
+    <row r="18" ht="46" customHeight="1">
+      <c r="A18" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Fond des séparations</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Les fins traits qui séparent chaque case du planning (lignes/colonnes de la grille) — techniquement, c'est un fond qui se voit juste dans l'écart de 1 pixel entre les cases.</t>
+        </is>
+      </c>
+      <c r="D18" s="64" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E18" s="65" t="inlineStr">
+        <is>
+          <t>#D7DAD2</t>
+        </is>
+      </c>
+      <c r="F18" s="66" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G18" s="67" t="inlineStr">
+        <is>
+          <t>#2B3540</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="n"/>
+      <c r="I18" s="13" t="inlineStr"/>
+    </row>
+    <row r="19" ht="46" customHeight="1">
+      <c r="A19" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Séparation renforcée</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Trait plus marqué entre deux semaines dans la grille, et piste des interrupteurs (cases à cocher "on/off") dans les formulaires.</t>
+        </is>
+      </c>
+      <c r="D19" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E19" s="69" t="inlineStr">
+        <is>
+          <t>#1A2129</t>
+        </is>
+      </c>
+      <c r="F19" s="70" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G19" s="71" t="inlineStr">
+        <is>
+          <t>#4A5661</t>
+        </is>
+      </c>
+      <c r="H19" s="12" t="n"/>
+      <c r="I19" s="13" t="inlineStr"/>
+    </row>
+    <row r="20" ht="46" customHeight="1">
+      <c r="A20" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Texte principal</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>La couleur de texte la plus utilisée — titres, noms, contenu des cases.</t>
+        </is>
+      </c>
+      <c r="D20" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E20" s="69" t="inlineStr">
+        <is>
+          <t>#1A2129</t>
+        </is>
+      </c>
+      <c r="F20" s="72" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G20" s="73" t="inlineStr">
+        <is>
+          <t>#EEF1F4</t>
+        </is>
+      </c>
+      <c r="H20" s="12" t="n"/>
+      <c r="I20" s="13" t="inlineStr"/>
+    </row>
+    <row r="21" ht="46" customHeight="1">
+      <c r="A21" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Texte secondaire</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Textes moins importants : sous-titres, dates, légendes.</t>
+        </is>
+      </c>
+      <c r="D21" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E21" s="75" t="inlineStr">
+        <is>
+          <t>#57616B</t>
+        </is>
+      </c>
+      <c r="F21" s="76" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G21" s="77" t="inlineStr">
+        <is>
+          <t>#9AA7B3</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="n"/>
+      <c r="I21" s="13" t="inlineStr"/>
+    </row>
+    <row r="22" ht="46" customHeight="1">
+      <c r="A22" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Texte discret / désactivé</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Textes encore plus effacés : compteurs, indications, éléments désactivés.</t>
+        </is>
+      </c>
+      <c r="D22" s="78" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E22" s="79" t="inlineStr">
+        <is>
+          <t>#8B93A0</t>
+        </is>
+      </c>
+      <c r="F22" s="80" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G22" s="81" t="inlineStr">
+        <is>
+          <t>#66717C</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="n"/>
+      <c r="I22" s="13" t="inlineStr"/>
+    </row>
+    <row r="23" ht="46" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Texte sur les tâches (bulles)</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Couleur du texte à l'intérieur des tâches/absences posées sur le planning.</t>
+        </is>
+      </c>
+      <c r="D23" s="82" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E23" s="83" t="inlineStr">
+        <is>
+          <t>#141814</t>
+        </is>
+      </c>
+      <c r="F23" s="82" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G23" s="83" t="inlineStr">
+        <is>
+          <t>#141814</t>
+        </is>
+      </c>
+      <c r="H23" s="12" t="n"/>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>Pas de variante sombre définie séparément (le texte est presque noir, légèrement transparent, ça passe dans les deux thèmes).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="46" customHeight="1">
+      <c r="A24" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Ombres</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>L'ombre portée sous les menus, fenêtres et cartes qui flottent au-dessus du planning.</t>
+        </is>
+      </c>
+      <c r="D24" s="84" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E24" s="85" t="inlineStr">
+        <is>
+          <t>#182129</t>
+        </is>
+      </c>
+      <c r="F24" s="86" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G24" s="87" t="inlineStr">
+        <is>
+          <t>#000000</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="n"/>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>Technique (juste une ombre plus ou moins sombre) — je te conseille de ne pas y toucher, sauf si tu trouves que les menus manquent de relief.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="88" t="n"/>
+      <c r="B25" s="89" t="inlineStr">
         <is>
           <t>Exemple (à effacer)</t>
         </is>
       </c>
-      <c r="C15" s="54" t="inlineStr">
+      <c r="C25" s="90" t="inlineStr">
         <is>
           <t>Ligne d'exemple : si tu veux regrouper deux lignes, écris le même mot dans leur case "Groupe", comme ici.</t>
         </is>
       </c>
-      <c r="D15" s="52" t="n"/>
-      <c r="E15" s="52" t="n"/>
-      <c r="F15" s="52" t="n"/>
-      <c r="G15" s="52" t="n"/>
-      <c r="H15" s="55" t="inlineStr">
+      <c r="D25" s="88" t="n"/>
+      <c r="E25" s="88" t="n"/>
+      <c r="F25" s="88" t="n"/>
+      <c r="G25" s="88" t="n"/>
+      <c r="H25" s="91" t="inlineStr">
         <is>
           <t>Rouge alertes</t>
         </is>
       </c>
-      <c r="I15" s="52" t="n"/>
+      <c r="I25" s="88" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0"/>

--- a/Claude outputs/Tableau-couleurs-Planning-Chantiers.xlsx
+++ b/Claude outputs/Tableau-couleurs-Planning-Chantiers.xlsx
@@ -89,7 +89,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="42">
+  <fills count="44">
     <fill>
       <patternFill/>
     </fill>
@@ -109,6 +109,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF9DB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3ECF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00223247"/>
       </patternFill>
     </fill>
     <fill>
@@ -321,7 +331,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -359,7 +369,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -371,11 +381,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -395,7 +405,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -431,11 +441,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="23" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="24" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="25" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -467,7 +477,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="32" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -475,7 +485,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="34" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="34" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -483,7 +493,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="36" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="36" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="36" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="37" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -504,6 +514,14 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="41" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="41" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="42" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="42" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="43" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -990,7 +1008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1098,36 +1116,40 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Erreur</t>
+          <t>Texte de l'onglet actif</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>Écran d'erreur au chargement, messages d'erreur.</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>#B3372F</t>
-        </is>
-      </c>
-      <c r="F3" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="G3" s="17" t="inlineStr">
-        <is>
-          <t>#E0685F</t>
+          <t>Le nom de la page actuellement ouverte, dans les onglets en haut (ou dans le menu "Pages" en bas sur téléphone).</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>#1F4D8F</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>#6FA6E8</t>
         </is>
       </c>
       <c r="H3" s="12" t="n"/>
-      <c r="I3" s="13" t="inlineStr"/>
+      <c r="I3" s="13" t="inlineStr">
+        <is>
+          <t>Même couleur que "Couleur principale de l'appli" ci-dessus — je remets une ligne à part pour que tu puisses la détacher si tu veux un rendu différent pour les onglets.</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="46" customHeight="1">
       <c r="A4" s="5" t="n">
@@ -1135,38 +1157,38 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Suppression / "important"</t>
+          <t>Fond de l'onglet actif</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Contour et texte des boutons "Supprimer", et texte des tâches marquées "importantes" sur une carte.</t>
-        </is>
-      </c>
-      <c r="D4" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E4" s="19" t="inlineStr">
-        <is>
-          <t>#93362B</t>
-        </is>
-      </c>
-      <c r="F4" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="G4" s="21" t="inlineStr">
-        <is>
-          <t>#F2A89C</t>
+          <t>Le fond ovale derrière le nom de la page actuellement ouverte, même endroit que la ligne au-dessus.</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>#E3ECF7</t>
+        </is>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G4" s="17" t="inlineStr">
+        <is>
+          <t>#223247</t>
         </is>
       </c>
       <c r="H4" s="12" t="n"/>
       <c r="I4" s="13" t="inlineStr">
         <is>
-          <t>Une seule couleur utilisée pour deux idées différentes (supprimer / important) — vois avec moi si tu veux les séparer.</t>
+          <t>Version pâle de la couleur principale, réutilisée aussi comme fond de survol sur beaucoup de boutons dans l'appli (pas seulement les onglets).</t>
         </is>
       </c>
     </row>
@@ -1176,40 +1198,36 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Étoile "marquer important" (activée)</t>
+          <t>Erreur</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Bouton étoile/marqueur sur une carte de tâche, quand il est activé.</t>
-        </is>
-      </c>
-      <c r="D5" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E5" s="23" t="inlineStr">
-        <is>
-          <t>#F2B134</t>
-        </is>
-      </c>
-      <c r="F5" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="G5" s="23" t="inlineStr">
-        <is>
-          <t>#F2B134</t>
+          <t>Écran d'erreur au chargement, messages d'erreur.</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="inlineStr">
+        <is>
+          <t>#B3372F</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G5" s="21" t="inlineStr">
+        <is>
+          <t>#E0685F</t>
         </is>
       </c>
       <c r="H5" s="12" t="n"/>
-      <c r="I5" s="13" t="inlineStr">
-        <is>
-          <t>Couleur différente de la ligne "Suppression / important" ci-dessus, alors que les deux parlent d'"important" — à toi de dire si ça doit rester distinct. Pas de variante sombre définie à part : reste identique en mode sombre actuellement.</t>
-        </is>
-      </c>
+      <c r="I5" s="13" t="inlineStr"/>
     </row>
     <row r="6" ht="46" customHeight="1">
       <c r="A6" s="5" t="n">
@@ -1217,22 +1235,22 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Absence (fond de case)</t>
+          <t>Suppression / "important"</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Fond des cases "absence" dans le planning, et le badge "type d'absence" sur une carte.</t>
-        </is>
-      </c>
-      <c r="D6" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E6" s="25" t="inlineStr">
-        <is>
-          <t>#F6C893</t>
+          <t>Contour et texte des boutons "Supprimer", et texte des tâches marquées "importantes" sur une carte.</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>#93362B</t>
         </is>
       </c>
       <c r="F6" s="24" t="inlineStr">
@@ -1242,13 +1260,13 @@
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>#F6C893</t>
+          <t>#F2A89C</t>
         </is>
       </c>
       <c r="H6" s="12" t="n"/>
       <c r="I6" s="13" t="inlineStr">
         <is>
-          <t>Pas de variante sombre définie séparément : garde la même couleur en mode sombre aujourd'hui.</t>
+          <t>Une seule couleur utilisée pour deux idées différentes (supprimer / important) — vois avec moi si tu veux les séparer.</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1276,12 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Jalon</t>
+          <t>Étoile "marquer important" (activée)</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Fond des jalons dans le planning, et le bouton "afficher les jalons" quand il est activé.</t>
+          <t>Bouton étoile/marqueur sur une carte de tâche, quand il est activé.</t>
         </is>
       </c>
       <c r="D7" s="26" t="inlineStr">
@@ -1273,7 +1291,7 @@
       </c>
       <c r="E7" s="27" t="inlineStr">
         <is>
-          <t>#D7CDF0</t>
+          <t>#F2B134</t>
         </is>
       </c>
       <c r="F7" s="26" t="inlineStr">
@@ -1283,13 +1301,13 @@
       </c>
       <c r="G7" s="27" t="inlineStr">
         <is>
-          <t>#D7CDF0</t>
+          <t>#F2B134</t>
         </is>
       </c>
       <c r="H7" s="12" t="n"/>
       <c r="I7" s="13" t="inlineStr">
         <is>
-          <t>Pas de variante sombre définie séparément non plus.</t>
+          <t>Couleur différente de la ligne "Suppression / important" ci-dessus, alors que les deux parlent d'"important" — à toi de dire si ça doit rester distinct. Pas de variante sombre définie à part : reste identique en mode sombre actuellement.</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1317,12 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Absence (fond de case)</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Fond des notes dans le planning, et le bouton "afficher les notes" quand il est activé.</t>
+          <t>Fond des cases "absence" dans le planning, et le badge "type d'absence" sur une carte.</t>
         </is>
       </c>
       <c r="D8" s="28" t="inlineStr">
@@ -1314,7 +1332,7 @@
       </c>
       <c r="E8" s="29" t="inlineStr">
         <is>
-          <t>#F7E6AB</t>
+          <t>#F6C893</t>
         </is>
       </c>
       <c r="F8" s="28" t="inlineStr">
@@ -1324,13 +1342,13 @@
       </c>
       <c r="G8" s="29" t="inlineStr">
         <is>
-          <t>#F7E6AB</t>
+          <t>#F6C893</t>
         </is>
       </c>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="13" t="inlineStr">
         <is>
-          <t>Pas de variante sombre définie séparément non plus.</t>
+          <t>Pas de variante sombre définie séparément : garde la même couleur en mode sombre aujourd'hui.</t>
         </is>
       </c>
     </row>
@@ -1340,12 +1358,12 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Halo de suppression</t>
+          <t>Jalon</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Contour qui apparaît autour du bouton "Supprimer" quand tu es sur le point de valider une suppression, et fond au survol du bouton "Effacer" dans un formulaire.</t>
+          <t>Fond des jalons dans le planning, et le bouton "afficher les jalons" quand il est activé.</t>
         </is>
       </c>
       <c r="D9" s="30" t="inlineStr">
@@ -1355,21 +1373,25 @@
       </c>
       <c r="E9" s="31" t="inlineStr">
         <is>
-          <t>#F6DCD7</t>
-        </is>
-      </c>
-      <c r="F9" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="G9" s="33" t="inlineStr">
-        <is>
-          <t>#4A2620</t>
+          <t>#D7CDF0</t>
+        </is>
+      </c>
+      <c r="F9" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G9" s="31" t="inlineStr">
+        <is>
+          <t>#D7CDF0</t>
         </is>
       </c>
       <c r="H9" s="12" t="n"/>
-      <c r="I9" s="13" t="inlineStr"/>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>Pas de variante sombre définie séparément non plus.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="46" customHeight="1">
       <c r="A10" s="5" t="n">
@@ -1377,36 +1399,40 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Case bloquée / avertissement</t>
+          <t>Note</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Fond des cases signalées comme bloquées/non disponibles dans le planning.</t>
-        </is>
-      </c>
-      <c r="D10" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E10" s="35" t="inlineStr">
-        <is>
-          <t>#F9D4B0</t>
-        </is>
-      </c>
-      <c r="F10" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="G10" s="37" t="inlineStr">
-        <is>
-          <t>#5A3110</t>
+          <t>Fond des notes dans le planning, et le bouton "afficher les notes" quand il est activé.</t>
+        </is>
+      </c>
+      <c r="D10" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E10" s="33" t="inlineStr">
+        <is>
+          <t>#F7E6AB</t>
+        </is>
+      </c>
+      <c r="F10" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G10" s="33" t="inlineStr">
+        <is>
+          <t>#F7E6AB</t>
         </is>
       </c>
       <c r="H10" s="12" t="n"/>
-      <c r="I10" s="13" t="inlineStr"/>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>Pas de variante sombre définie séparément non plus.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="46" customHeight="1">
       <c r="A11" s="5" t="n">
@@ -1414,32 +1440,32 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Sélection en cours (ajout)</t>
+          <t>Halo de suppression</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Surbrillance verte quand tu es en train d'étendre une sélection de cases dans le planning.</t>
-        </is>
-      </c>
-      <c r="D11" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E11" s="39" t="inlineStr">
-        <is>
-          <t>#CDEECC</t>
-        </is>
-      </c>
-      <c r="F11" s="40" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="G11" s="41" t="inlineStr">
-        <is>
-          <t>#1C3A20</t>
+          <t>Contour qui apparaît autour du bouton "Supprimer" quand tu es sur le point de valider une suppression, et fond au survol du bouton "Effacer" dans un formulaire.</t>
+        </is>
+      </c>
+      <c r="D11" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E11" s="35" t="inlineStr">
+        <is>
+          <t>#F6DCD7</t>
+        </is>
+      </c>
+      <c r="F11" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G11" s="37" t="inlineStr">
+        <is>
+          <t>#4A2620</t>
         </is>
       </c>
       <c r="H11" s="12" t="n"/>
@@ -1451,32 +1477,32 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Week-end (fond de colonne)</t>
+          <t>Case bloquée / avertissement</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Fond des colonnes samedi/dimanche dans le planning.</t>
-        </is>
-      </c>
-      <c r="D12" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E12" s="43" t="inlineStr">
-        <is>
-          <t>#CDCFC9</t>
-        </is>
-      </c>
-      <c r="F12" s="44" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="G12" s="45" t="inlineStr">
-        <is>
-          <t>#232B34</t>
+          <t>Fond des cases signalées comme bloquées/non disponibles dans le planning.</t>
+        </is>
+      </c>
+      <c r="D12" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E12" s="39" t="inlineStr">
+        <is>
+          <t>#F9D4B0</t>
+        </is>
+      </c>
+      <c r="F12" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G12" s="41" t="inlineStr">
+        <is>
+          <t>#5A3110</t>
         </is>
       </c>
       <c r="H12" s="12" t="n"/>
@@ -1488,40 +1514,36 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Statut "confirmé"</t>
+          <t>Sélection en cours (ajout)</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Couleur réservée pour un badge "confirmé" — je n'ai pas trouvé où elle s'affiche actuellement dans l'appli.</t>
-        </is>
-      </c>
-      <c r="D13" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E13" s="47" t="inlineStr">
-        <is>
-          <t>#CDF1EA</t>
-        </is>
-      </c>
-      <c r="F13" s="48" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="G13" s="49" t="inlineStr">
-        <is>
-          <t>#123F38</t>
+          <t>Surbrillance verte quand tu es en train d'étendre une sélection de cases dans le planning.</t>
+        </is>
+      </c>
+      <c r="D13" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E13" s="43" t="inlineStr">
+        <is>
+          <t>#CDEECC</t>
+        </is>
+      </c>
+      <c r="F13" s="44" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G13" s="45" t="inlineStr">
+        <is>
+          <t>#1C3A20</t>
         </is>
       </c>
       <c r="H13" s="12" t="n"/>
-      <c r="I13" s="13" t="inlineStr">
-        <is>
-          <t>Possiblement plus utilisée nulle part actuellement — dis-moi si tu veux la garder ou si on peut l'enlever.</t>
-        </is>
-      </c>
+      <c r="I13" s="13" t="inlineStr"/>
     </row>
     <row r="14" ht="46" customHeight="1">
       <c r="A14" s="5" t="n">
@@ -1529,40 +1551,36 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Point de synchronisation</t>
+          <t>Week-end (fond de colonne)</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Petit point en haut de l'écran qui clignote pour indiquer que l'appli est bien connectée.</t>
-        </is>
-      </c>
-      <c r="D14" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E14" s="51" t="inlineStr">
-        <is>
-          <t>#3FA15A</t>
-        </is>
-      </c>
-      <c r="F14" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="G14" s="51" t="inlineStr">
-        <is>
-          <t>#3FA15A</t>
+          <t>Fond des colonnes samedi/dimanche dans le planning.</t>
+        </is>
+      </c>
+      <c r="D14" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E14" s="47" t="inlineStr">
+        <is>
+          <t>#CDCFC9</t>
+        </is>
+      </c>
+      <c r="F14" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G14" s="49" t="inlineStr">
+        <is>
+          <t>#232B34</t>
         </is>
       </c>
       <c r="H14" s="12" t="n"/>
-      <c r="I14" s="13" t="inlineStr">
-        <is>
-          <t>Indicateur technique (vert = connecté) — je te le mets pour être complet, mais je te conseille de ne pas y toucher.</t>
-        </is>
-      </c>
+      <c r="I14" s="13" t="inlineStr"/>
     </row>
     <row r="15" ht="46" customHeight="1">
       <c r="A15" s="5" t="n">
@@ -1570,36 +1588,40 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Fond général de l'appli</t>
+          <t>Statut "confirmé"</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Le fond derrière tout, tout en haut de l'écran (bandeau du haut, zone au-dessus du planning).</t>
-        </is>
-      </c>
-      <c r="D15" s="52" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E15" s="53" t="inlineStr">
-        <is>
-          <t>#FFFFFF</t>
-        </is>
-      </c>
-      <c r="F15" s="54" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="G15" s="55" t="inlineStr">
-        <is>
-          <t>#10161D</t>
+          <t>Couleur réservée pour un badge "confirmé" — je n'ai pas trouvé où elle s'affiche actuellement dans l'appli.</t>
+        </is>
+      </c>
+      <c r="D15" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E15" s="51" t="inlineStr">
+        <is>
+          <t>#CDF1EA</t>
+        </is>
+      </c>
+      <c r="F15" s="52" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G15" s="53" t="inlineStr">
+        <is>
+          <t>#123F38</t>
         </is>
       </c>
       <c r="H15" s="12" t="n"/>
-      <c r="I15" s="13" t="inlineStr"/>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>Possiblement plus utilisée nulle part actuellement — dis-moi si tu veux la garder ou si on peut l'enlever.</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="46" customHeight="1">
       <c r="A16" s="5" t="n">
@@ -1607,36 +1629,40 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Fond des cases</t>
+          <t>Point de synchronisation</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Le fond de TOUTES les cases du planning, des en-têtes de colonnes (jours) et des étiquettes de ligne (noms des personnes) — la couleur la plus présente de la grille.</t>
-        </is>
-      </c>
-      <c r="D16" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E16" s="57" t="inlineStr">
-        <is>
-          <t>#DFDFDF</t>
-        </is>
-      </c>
-      <c r="F16" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="G16" s="59" t="inlineStr">
-        <is>
-          <t>#1C2530</t>
+          <t>Petit point en haut de l'écran qui clignote pour indiquer que l'appli est bien connectée.</t>
+        </is>
+      </c>
+      <c r="D16" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E16" s="55" t="inlineStr">
+        <is>
+          <t>#3FA15A</t>
+        </is>
+      </c>
+      <c r="F16" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G16" s="55" t="inlineStr">
+        <is>
+          <t>#3FA15A</t>
         </is>
       </c>
       <c r="H16" s="12" t="n"/>
-      <c r="I16" s="13" t="inlineStr"/>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>Indicateur technique (vert = connecté) — je te le mets pour être complet, mais je te conseille de ne pas y toucher.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="46" customHeight="1">
       <c r="A17" s="5" t="n">
@@ -1644,32 +1670,32 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Fond secondaire (coin, étiquettes spéciales)</t>
+          <t>Fond général de l'appli</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Fond du coin en haut à gauche de la grille, des lignes "spéciales" (section Personnel/Intervenants), et de la petite ligne matin/après-midi en mode compact.</t>
-        </is>
-      </c>
-      <c r="D17" s="60" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E17" s="61" t="inlineStr">
-        <is>
-          <t>#F0F0F0</t>
-        </is>
-      </c>
-      <c r="F17" s="62" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="G17" s="63" t="inlineStr">
-        <is>
-          <t>#171F28</t>
+          <t>Le fond derrière tout, tout en haut de l'écran (bandeau du haut, zone au-dessus du planning).</t>
+        </is>
+      </c>
+      <c r="D17" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E17" s="57" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="F17" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G17" s="59" t="inlineStr">
+        <is>
+          <t>#10161D</t>
         </is>
       </c>
       <c r="H17" s="12" t="n"/>
@@ -1681,32 +1707,32 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Fond des séparations</t>
+          <t>Fond des cases</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Les fins traits qui séparent chaque case du planning (lignes/colonnes de la grille) — techniquement, c'est un fond qui se voit juste dans l'écart de 1 pixel entre les cases.</t>
-        </is>
-      </c>
-      <c r="D18" s="64" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E18" s="65" t="inlineStr">
-        <is>
-          <t>#D7DAD2</t>
-        </is>
-      </c>
-      <c r="F18" s="66" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="G18" s="67" t="inlineStr">
-        <is>
-          <t>#2B3540</t>
+          <t>Le fond de TOUTES les cases du planning, des en-têtes de colonnes (jours) et des étiquettes de ligne (noms des personnes) — la couleur la plus présente de la grille.</t>
+        </is>
+      </c>
+      <c r="D18" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E18" s="61" t="inlineStr">
+        <is>
+          <t>#DFDFDF</t>
+        </is>
+      </c>
+      <c r="F18" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G18" s="63" t="inlineStr">
+        <is>
+          <t>#1C2530</t>
         </is>
       </c>
       <c r="H18" s="12" t="n"/>
@@ -1718,32 +1744,32 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Séparation renforcée</t>
+          <t>Fond secondaire (coin, étiquettes spéciales)</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Trait plus marqué entre deux semaines dans la grille, et piste des interrupteurs (cases à cocher "on/off") dans les formulaires.</t>
-        </is>
-      </c>
-      <c r="D19" s="68" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E19" s="69" t="inlineStr">
-        <is>
-          <t>#1A2129</t>
-        </is>
-      </c>
-      <c r="F19" s="70" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="G19" s="71" t="inlineStr">
-        <is>
-          <t>#4A5661</t>
+          <t>Fond du coin en haut à gauche de la grille, des lignes "spéciales" (section Personnel/Intervenants), et de la petite ligne matin/après-midi en mode compact.</t>
+        </is>
+      </c>
+      <c r="D19" s="64" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E19" s="65" t="inlineStr">
+        <is>
+          <t>#F0F0F0</t>
+        </is>
+      </c>
+      <c r="F19" s="66" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G19" s="67" t="inlineStr">
+        <is>
+          <t>#171F28</t>
         </is>
       </c>
       <c r="H19" s="12" t="n"/>
@@ -1755,12 +1781,12 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Texte principal</t>
+          <t>Fond des séparations</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>La couleur de texte la plus utilisée — titres, noms, contenu des cases.</t>
+          <t>Les fins traits qui séparent chaque case du planning (lignes/colonnes de la grille) — techniquement, c'est un fond qui se voit juste dans l'écart de 1 pixel entre les cases.</t>
         </is>
       </c>
       <c r="D20" s="68" t="inlineStr">
@@ -1770,17 +1796,17 @@
       </c>
       <c r="E20" s="69" t="inlineStr">
         <is>
-          <t>#1A2129</t>
-        </is>
-      </c>
-      <c r="F20" s="72" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="G20" s="73" t="inlineStr">
-        <is>
-          <t>#EEF1F4</t>
+          <t>#D7DAD2</t>
+        </is>
+      </c>
+      <c r="F20" s="70" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G20" s="71" t="inlineStr">
+        <is>
+          <t>#2B3540</t>
         </is>
       </c>
       <c r="H20" s="12" t="n"/>
@@ -1792,32 +1818,32 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Texte secondaire</t>
+          <t>Séparation renforcée</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Textes moins importants : sous-titres, dates, légendes.</t>
-        </is>
-      </c>
-      <c r="D21" s="74" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E21" s="75" t="inlineStr">
-        <is>
-          <t>#57616B</t>
-        </is>
-      </c>
-      <c r="F21" s="76" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="G21" s="77" t="inlineStr">
-        <is>
-          <t>#9AA7B3</t>
+          <t>Trait plus marqué entre deux semaines dans la grille, et piste des interrupteurs (cases à cocher "on/off") dans les formulaires.</t>
+        </is>
+      </c>
+      <c r="D21" s="72" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E21" s="73" t="inlineStr">
+        <is>
+          <t>#1A2129</t>
+        </is>
+      </c>
+      <c r="F21" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G21" s="75" t="inlineStr">
+        <is>
+          <t>#4A5661</t>
         </is>
       </c>
       <c r="H21" s="12" t="n"/>
@@ -1829,32 +1855,32 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Texte discret / désactivé</t>
+          <t>Texte principal</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Textes encore plus effacés : compteurs, indications, éléments désactivés.</t>
-        </is>
-      </c>
-      <c r="D22" s="78" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E22" s="79" t="inlineStr">
-        <is>
-          <t>#8B93A0</t>
-        </is>
-      </c>
-      <c r="F22" s="80" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="G22" s="81" t="inlineStr">
-        <is>
-          <t>#66717C</t>
+          <t>La couleur de texte la plus utilisée — titres, noms, contenu des cases.</t>
+        </is>
+      </c>
+      <c r="D22" s="72" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E22" s="73" t="inlineStr">
+        <is>
+          <t>#1A2129</t>
+        </is>
+      </c>
+      <c r="F22" s="76" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G22" s="77" t="inlineStr">
+        <is>
+          <t>#EEF1F4</t>
         </is>
       </c>
       <c r="H22" s="12" t="n"/>
@@ -1866,40 +1892,36 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Texte sur les tâches (bulles)</t>
+          <t>Texte secondaire</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Couleur du texte à l'intérieur des tâches/absences posées sur le planning.</t>
-        </is>
-      </c>
-      <c r="D23" s="82" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E23" s="83" t="inlineStr">
-        <is>
-          <t>#141814</t>
-        </is>
-      </c>
-      <c r="F23" s="82" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="G23" s="83" t="inlineStr">
-        <is>
-          <t>#141814</t>
+          <t>Textes moins importants : sous-titres, dates, légendes.</t>
+        </is>
+      </c>
+      <c r="D23" s="78" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E23" s="79" t="inlineStr">
+        <is>
+          <t>#57616B</t>
+        </is>
+      </c>
+      <c r="F23" s="80" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G23" s="81" t="inlineStr">
+        <is>
+          <t>#9AA7B3</t>
         </is>
       </c>
       <c r="H23" s="12" t="n"/>
-      <c r="I23" s="13" t="inlineStr">
-        <is>
-          <t>Pas de variante sombre définie séparément (le texte est presque noir, légèrement transparent, ça passe dans les deux thèmes).</t>
-        </is>
-      </c>
+      <c r="I23" s="13" t="inlineStr"/>
     </row>
     <row r="24" ht="46" customHeight="1">
       <c r="A24" s="5" t="n">
@@ -1907,63 +1929,141 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
+          <t>Texte discret / désactivé</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Textes encore plus effacés : compteurs, indications, éléments désactivés.</t>
+        </is>
+      </c>
+      <c r="D24" s="82" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E24" s="83" t="inlineStr">
+        <is>
+          <t>#8B93A0</t>
+        </is>
+      </c>
+      <c r="F24" s="84" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G24" s="85" t="inlineStr">
+        <is>
+          <t>#66717C</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="n"/>
+      <c r="I24" s="13" t="inlineStr"/>
+    </row>
+    <row r="25" ht="46" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Texte sur les tâches (bulles)</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Couleur du texte à l'intérieur des tâches/absences posées sur le planning.</t>
+        </is>
+      </c>
+      <c r="D25" s="86" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E25" s="87" t="inlineStr">
+        <is>
+          <t>#141814</t>
+        </is>
+      </c>
+      <c r="F25" s="86" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G25" s="87" t="inlineStr">
+        <is>
+          <t>#141814</t>
+        </is>
+      </c>
+      <c r="H25" s="12" t="n"/>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>Pas de variante sombre définie séparément (le texte est presque noir, légèrement transparent, ça passe dans les deux thèmes).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="46" customHeight="1">
+      <c r="A26" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
           <t>Ombres</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>L'ombre portée sous les menus, fenêtres et cartes qui flottent au-dessus du planning.</t>
         </is>
       </c>
-      <c r="D24" s="84" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E24" s="85" t="inlineStr">
+      <c r="D26" s="88" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E26" s="89" t="inlineStr">
         <is>
           <t>#182129</t>
         </is>
       </c>
-      <c r="F24" s="86" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="G24" s="87" t="inlineStr">
+      <c r="F26" s="90" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G26" s="91" t="inlineStr">
         <is>
           <t>#000000</t>
         </is>
       </c>
-      <c r="H24" s="12" t="n"/>
-      <c r="I24" s="13" t="inlineStr">
+      <c r="H26" s="12" t="n"/>
+      <c r="I26" s="13" t="inlineStr">
         <is>
           <t>Technique (juste une ombre plus ou moins sombre) — je te conseille de ne pas y toucher, sauf si tu trouves que les menus manquent de relief.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="88" t="n"/>
-      <c r="B25" s="89" t="inlineStr">
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="92" t="n"/>
+      <c r="B27" s="93" t="inlineStr">
         <is>
           <t>Exemple (à effacer)</t>
         </is>
       </c>
-      <c r="C25" s="90" t="inlineStr">
+      <c r="C27" s="94" t="inlineStr">
         <is>
           <t>Ligne d'exemple : si tu veux regrouper deux lignes, écris le même mot dans leur case "Groupe", comme ici.</t>
         </is>
       </c>
-      <c r="D25" s="88" t="n"/>
-      <c r="E25" s="88" t="n"/>
-      <c r="F25" s="88" t="n"/>
-      <c r="G25" s="88" t="n"/>
-      <c r="H25" s="91" t="inlineStr">
+      <c r="D27" s="92" t="n"/>
+      <c r="E27" s="92" t="n"/>
+      <c r="F27" s="92" t="n"/>
+      <c r="G27" s="92" t="n"/>
+      <c r="H27" s="95" t="inlineStr">
         <is>
           <t>Rouge alertes</t>
         </is>
       </c>
-      <c r="I25" s="88" t="n"/>
+      <c r="I27" s="92" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0"/>
